--- a/Project File Main.xlsx
+++ b/Project File Main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcc17fd4f780ddee/Documents/Python Project File/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C42497-6DD7-4859-B8A9-7C28E5C9BA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{96C42497-6DD7-4859-B8A9-7C28E5C9BA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD22AC3C-AA0C-48FA-8F5F-23AD6FDD0980}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -193,9 +193,6 @@
     <t>Siddharth</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>CAP-776/D1P2636</t>
   </si>
   <si>
@@ -350,6 +347,9 @@
   </si>
   <si>
     <t>Productive day with focused study, coding practice, and revision of important topics.</t>
+  </si>
+  <si>
+    <t>Sepetember</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1054,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1062,7 +1062,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1211,13 +1211,13 @@
         <v>49</v>
       </c>
       <c r="L7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1263,7 +1263,7 @@
         <v>51</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1300,16 +1300,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L9" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N9" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1355,7 +1355,7 @@
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1392,16 +1392,16 @@
         <v>0</v>
       </c>
       <c r="K11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="M11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1438,16 +1438,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>62</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1487,13 +1487,13 @@
         <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1530,16 +1530,16 @@
         <v>0</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="17" t="s">
         <v>76</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1576,16 +1576,16 @@
         <v>0</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1628,10 +1628,10 @@
         <v>50</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1668,16 +1668,16 @@
         <v>0</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L17" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1714,16 +1714,16 @@
         <v>0</v>
       </c>
       <c r="K18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="M18" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="K19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L19" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L19" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="M19" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1815,7 +1815,7 @@
         <v>51</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1852,16 +1852,16 @@
         <v>0</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L21" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1907,7 +1907,7 @@
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1950,10 +1950,10 @@
         <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1993,13 +1993,13 @@
         <v>49</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>50</v>
@@ -2045,7 +2045,7 @@
         <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2082,16 +2082,16 @@
         <v>0</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2135,7 +2135,7 @@
         <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2176,10 +2176,10 @@
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>50</v>
@@ -2223,7 +2223,7 @@
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2261,13 +2261,13 @@
         <v>49</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="K31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L31" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L31" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="M31" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2346,16 +2346,16 @@
         <v>0</v>
       </c>
       <c r="K32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L32" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>62</v>
       </c>
       <c r="M32" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2399,7 +2399,7 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2434,16 +2434,16 @@
         <v>0</v>
       </c>
       <c r="K34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L34" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N34" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2487,7 +2487,7 @@
         <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2528,10 +2528,10 @@
         <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2572,10 +2572,10 @@
         <v>50</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2610,16 +2610,16 @@
         <v>0</v>
       </c>
       <c r="K38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L38" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L38" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="M38" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>50</v>
@@ -2663,7 +2663,7 @@
         <v>51</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2707,7 +2707,7 @@
         <v>51</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2742,16 +2742,16 @@
         <v>0</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2795,7 +2795,7 @@
         <v>51</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2833,13 +2833,13 @@
         <v>49</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2880,10 +2880,10 @@
         <v>50</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2918,16 +2918,16 @@
         <v>0</v>
       </c>
       <c r="K45" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L45" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L45" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="M45" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2962,16 +2962,16 @@
         <v>0</v>
       </c>
       <c r="K46" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L46" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="L46" s="16" t="s">
-        <v>62</v>
       </c>
       <c r="M46" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3015,7 +3015,7 @@
         <v>51</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -3050,16 +3050,16 @@
         <v>0</v>
       </c>
       <c r="K48" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M48" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L48" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M48" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N48" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -3097,13 +3097,13 @@
         <v>49</v>
       </c>
       <c r="L49" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M49" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N49" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -3147,7 +3147,7 @@
         <v>51</v>
       </c>
       <c r="N50" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -3182,16 +3182,16 @@
         <v>0</v>
       </c>
       <c r="K51" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L51" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L51" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="M51" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N51" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
